--- a/ASVS-checklist-en.xlsx
+++ b/ASVS-checklist-en.xlsx
@@ -393,7 +393,7 @@
       <row>20</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="7200000"/>
+    <ext cx="8640000" cy="6120000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
